--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487433_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487433_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6993</v>
+        <v>6.7552</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5324</v>
+        <v>5.4624</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1669</v>
+        <v>1.2928</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6949</v>
+        <v>2.9142</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0783</v>
+        <v>2.1467</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6166</v>
+        <v>0.7675</v>
       </c>
       <c r="J2" t="n">
-        <v>4.471</v>
+        <v>5.4579</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2085</v>
+        <v>3.0946</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2625</v>
+        <v>2.3634</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7761</v>
+        <v>-2.5437</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1302</v>
+        <v>-0.9479</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6459</v>
+        <v>-1.5958</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.1543</v>
+        <v>2.546</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.1128</v>
+        <v>-1.1751</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9585</v>
+        <v>3.7211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8994</v>
+        <v>-0.197</v>
       </c>
       <c r="T2" t="n">
-        <v>1.915</v>
+        <v>0.3535</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0155</v>
+        <v>-0.5505</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2593</v>
+        <v>1.492</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2593</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0853</v>
+        <v>5.5369</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7738</v>
+        <v>4.0808</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3115</v>
+        <v>1.4561</v>
       </c>
       <c r="G3" t="n">
         <v>5.2374</v>
@@ -688,13 +688,13 @@
         <v>3.3294</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3018</v>
+        <v>0.7534</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0465</v>
+        <v>0.3535</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2553</v>
+        <v>0.3999</v>
       </c>
       <c r="V3" t="n">
         <v>-1.8249</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.068</v>
+        <v>5.3598</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0959</v>
+        <v>4.4067</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9721</v>
+        <v>0.953</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9142</v>
+        <v>3.6949</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1467</v>
+        <v>3.0783</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7675</v>
+        <v>0.6166</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4579</v>
+        <v>4.471</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0946</v>
+        <v>3.2085</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3634</v>
+        <v>1.2625</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5437</v>
+        <v>-0.7761</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9479</v>
+        <v>-0.1302</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5958</v>
+        <v>-0.6459</v>
       </c>
       <c r="P4" t="n">
-        <v>2.546</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1751</v>
+        <v>-4.1128</v>
       </c>
       <c r="R4" t="n">
-        <v>3.7211</v>
+        <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8842</v>
+        <v>0.5599</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0129</v>
+        <v>0.7893</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8713</v>
+        <v>-0.2294</v>
       </c>
       <c r="V4" t="n">
-        <v>1.492</v>
+        <v>3.2593</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8260999999999999</v>
+        <v>3.2593</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1582</v>
+        <v>4.069</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4224</v>
+        <v>-0.1323</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7359</v>
+        <v>4.2013</v>
       </c>
       <c r="G5" t="n">
         <v>0.9293</v>
@@ -844,13 +844,13 @@
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1079</v>
+        <v>1.0187</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2327</v>
+        <v>0.6781</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8752</v>
+        <v>0.3405</v>
       </c>
       <c r="V5" t="n">
         <v>2.7086</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5923</v>
+        <v>3.8656</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6569</v>
+        <v>4.7163</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0646</v>
+        <v>-0.8507</v>
       </c>
       <c r="G6" t="n">
         <v>1.6695</v>
@@ -922,13 +922,13 @@
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4273</v>
+        <v>-0.1541</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0882</v>
+        <v>0.1476</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.3017</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7197</v>
+        <v>2.0021</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6274</v>
+        <v>0.4821</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0923</v>
+        <v>1.52</v>
       </c>
       <c r="G7" t="n">
         <v>4.1612</v>
@@ -1000,13 +1000,13 @@
         <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4036</v>
+        <v>-0.1212</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2664</v>
+        <v>0.1212</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.67</v>
+        <v>-0.2423</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9491</v>
+        <v>-1.6596</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7395</v>
+        <v>-1.6371</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2096</v>
+        <v>-0.0225</v>
       </c>
       <c r="G8" t="n">
         <v>-0.43</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.2504</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.421</v>
+        <v>-0.2339</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1286</v>
+        <v>-1.6879</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5044</v>
+        <v>-1.1974</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6241</v>
+        <v>-0.4905</v>
       </c>
       <c r="G9" t="n">
         <v>0.7765</v>
@@ -1156,13 +1156,13 @@
         <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1389</v>
+        <v>-0.6983</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6534</v>
+        <v>-0.3464</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4855</v>
+        <v>-0.3518</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1578</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3574</v>
+        <v>-2.2283</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6784</v>
+        <v>-1.5761</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.6522</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1231</v>
@@ -1234,13 +1234,13 @@
         <v>0.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4509</v>
+        <v>-0.3219</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3321</v>
+        <v>-0.3054</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2684</v>
+        <v>-3.9242</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1943</v>
+        <v>-1.9302</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0742</v>
+        <v>-1.994</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3408</v>
@@ -1312,13 +1312,13 @@
         <v>0.5875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7893</v>
+        <v>-0.4451</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.297</v>
+        <v>-0.0329</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4923</v>
+        <v>-0.4121</v>
       </c>
       <c r="V11" t="n">
         <v>-1.7673</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9078</v>
+        <v>-5.08</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.8871</v>
+        <v>-5.2731</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0207</v>
+        <v>0.1931</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4697</v>
@@ -1390,13 +1390,13 @@
         <v>2.1543</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2043</v>
+        <v>-0.3764</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6952</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5091</v>
+        <v>-0.2952</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2754</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.7115</v>
+        <v>13.0086</v>
       </c>
       <c r="E13" t="n">
-        <v>7.105099999999998</v>
+        <v>7.4021</v>
       </c>
       <c r="F13" t="n">
-        <v>5.606600000000002</v>
+        <v>5.606400000000001</v>
       </c>
       <c r="G13" t="n">
         <v>15.0194</v>
@@ -1447,7 +1447,7 @@
         <v>15.6289</v>
       </c>
       <c r="L13" t="n">
-        <v>5.250399999999999</v>
+        <v>5.250400000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-5.8598</v>
@@ -1468,10 +1468,10 @@
         <v>21.5432</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5291999999999998</v>
+        <v>-0.2324000000000005</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6527</v>
+        <v>1.9497</v>
       </c>
       <c r="U13" t="n">
         <v>-2.1819</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.2797</v>
+        <v>6.0395</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8192</v>
+        <v>3.9772</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4605</v>
+        <v>2.0624</v>
       </c>
       <c r="G14" t="n">
         <v>3.5291</v>
@@ -1546,13 +1546,13 @@
         <v>3.5253</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4177</v>
+        <v>1.1774</v>
       </c>
       <c r="T14" t="n">
-        <v>2.923</v>
+        <v>1.081</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4946</v>
+        <v>0.0965</v>
       </c>
       <c r="V14" t="n">
         <v>0.9412</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1781</v>
+        <v>0.138</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8489</v>
+        <v>0.3367</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6708</v>
+        <v>-0.1987</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0144</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8724</v>
+        <v>-0.7339</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.142</v>
+        <v>-0.2273</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0177</v>
+        <v>0.1221</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9628</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0549</v>
+        <v>0.0404</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0322</v>
+        <v>-1.0833</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8353</v>
+        <v>-0.8156</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1969</v>
+        <v>-0.2677</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.546</v>
+        <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.181</v>
+        <v>-0.0759</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6099</v>
+        <v>0.2147</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5711000000000001</v>
+        <v>-0.2905</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6198</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3756</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4032</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1749</v>
+        <v>1.9911</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2282</v>
+        <v>-1.9811</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9612000000000001</v>
+        <v>0.4666</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7339</v>
+        <v>0.4158</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2273</v>
+        <v>0.0508</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1221</v>
+        <v>1.3384</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08169999999999999</v>
+        <v>1.298</v>
       </c>
       <c r="L16" t="n">
         <v>0.0404</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0833</v>
+        <v>-0.8718</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8156</v>
+        <v>-0.8822</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2677</v>
+        <v>0.0104</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6171</v>
+        <v>-0.1144</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.297</v>
+        <v>0.14</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3201</v>
+        <v>-0.2544</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9297</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4217</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7893</v>
+        <v>-0.3741</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2748</v>
+        <v>1.6442</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0641</v>
+        <v>-2.0183</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4666</v>
+        <v>-2.0144</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4158</v>
+        <v>-0.8724</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0508</v>
+        <v>-1.142</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3384</v>
+        <v>1.0177</v>
       </c>
       <c r="K17" t="n">
-        <v>1.298</v>
+        <v>0.9628</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0404</v>
+        <v>0.0549</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8718</v>
+        <v>-3.0322</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8822</v>
+        <v>-1.8353</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0104</v>
+        <v>-1.1969</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5668</v>
+        <v>2.546</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9137</v>
+        <v>0.6289</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5764</v>
+        <v>0.4052</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3374</v>
+        <v>0.2236</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9297</v>
+        <v>0.6198</v>
       </c>
       <c r="W17" t="n">
-        <v>1.492</v>
+        <v>2.3756</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4217</v>
+        <v>-1.7558</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GOMEZ CABAL</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0013</v>
+        <v>-0.7006</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3779</v>
+        <v>0.3432</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3766</v>
+        <v>-1.0438</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.9832</v>
+        <v>-2.1347</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4111</v>
+        <v>-0.6897</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5721000000000001</v>
+        <v>-1.4449</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1144</v>
+        <v>0.4267</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5768</v>
+        <v>0.9424</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5376</v>
+        <v>-0.5158</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8687</v>
+        <v>-2.5613</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8342</v>
+        <v>-1.6322</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9655</v>
+        <v>-0.9292</v>
       </c>
       <c r="P18" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.1543</v>
+      </c>
+      <c r="R18" t="n">
         <v>2.546</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.1751</v>
-      </c>
-      <c r="R18" t="n">
-        <v>3.7211</v>
-      </c>
       <c r="S18" t="n">
-        <v>-0.0135</v>
+        <v>-0.1742</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9116</v>
+        <v>-0.0294</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9251</v>
+        <v>-0.1448</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5507</v>
+        <v>1.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1003</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5507</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>A. GOMEZ CABAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0435</v>
+        <v>-0.8198</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2409</v>
+        <v>-2.7873</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2844</v>
+        <v>1.9675</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1347</v>
+        <v>-2.9832</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6897</v>
+        <v>-2.4111</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4449</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4267</v>
+        <v>-2.1144</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9424</v>
+        <v>-0.5768</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5158</v>
+        <v>-1.5376</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.5613</v>
+        <v>-0.8687</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6322</v>
+        <v>-1.8342</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9292</v>
+        <v>0.9655</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3917</v>
+        <v>2.546</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1543</v>
+        <v>-1.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>2.546</v>
+        <v>3.7211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5172</v>
+        <v>0.1681</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1317</v>
+        <v>0.5023</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3854</v>
+        <v>-0.3342</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2166</v>
+        <v>-0.5507</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1003</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8837</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3736</v>
+        <v>-1.8527</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0561</v>
+        <v>0.2509</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3175</v>
+        <v>-2.1037</v>
       </c>
       <c r="G20" t="n">
         <v>1.8083</v>
@@ -2014,13 +2014,13 @@
         <v>3.3294</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5944</v>
+        <v>-0.0735</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3517</v>
+        <v>-0.0447</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2427</v>
+        <v>-0.0288</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8249</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.622</v>
+        <v>-2.2883</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0757</v>
+        <v>-1.7687</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5196</v>
       </c>
       <c r="G21" t="n">
         <v>-2.924</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5344</v>
+        <v>-0.2007</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4993</v>
+        <v>-0.1923</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0351</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>1.2281</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4916</v>
+        <v>-2.7098</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1987</v>
+        <v>-3.687</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7071</v>
+        <v>0.9772</v>
       </c>
       <c r="G22" t="n">
         <v>-2.0848</v>
@@ -2170,13 +2170,13 @@
         <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0266</v>
+        <v>-0.2448</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3564</v>
+        <v>0.1553</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6702</v>
+        <v>-0.4001</v>
       </c>
       <c r="V22" t="n">
         <v>0.0115</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.868</v>
+        <v>-4.1261</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.279</v>
+        <v>-2.4837</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.589</v>
+        <v>-1.6424</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9833</v>
@@ -2248,13 +2248,13 @@
         <v>0.9792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3319</v>
+        <v>0.0738</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1235</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2084</v>
+        <v>0.155</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5768</v>
+        <v>-5.3454</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6277</v>
+        <v>-3.423</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9491</v>
+        <v>-1.9224</v>
       </c>
       <c r="G24" t="n">
         <v>-4.738</v>
@@ -2326,13 +2326,13 @@
         <v>1.9585</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1845</v>
+        <v>0.0469</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1735</v>
+        <v>0.0312</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.011</v>
+        <v>0.0157</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6544</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.7115</v>
+        <v>-12.0293</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.606199999999999</v>
+        <v>-5.606399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.1052</v>
+        <v>-6.4229</v>
       </c>
       <c r="G25" t="n">
         <v>-15.0196</v>
@@ -2404,13 +2404,13 @@
         <v>24.481</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5291999999999999</v>
+        <v>1.2116</v>
       </c>
       <c r="T25" t="n">
-        <v>2.182</v>
+        <v>2.1821</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6529</v>
+        <v>-0.9703999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-1.1591</v>
